--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484070_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484070_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3336</v>
+        <v>4.0787</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3723</v>
+        <v>4.454</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0387</v>
+        <v>-0.3754</v>
       </c>
       <c r="G2" t="n">
         <v>1.9424</v>
@@ -610,13 +610,13 @@
         <v>1.7855</v>
       </c>
       <c r="S2" t="n">
-        <v>2.876</v>
+        <v>1.6211</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4941</v>
+        <v>1.5758</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3819</v>
+        <v>0.0452</v>
       </c>
       <c r="V2" t="n">
         <v>0.912</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1835</v>
+        <v>2.8084</v>
       </c>
       <c r="E3" t="n">
-        <v>4.642</v>
+        <v>4.8461</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.4585</v>
+        <v>-2.0377</v>
       </c>
       <c r="G3" t="n">
         <v>2.0446</v>
@@ -688,13 +688,13 @@
         <v>1.1903</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1389</v>
+        <v>0.7638</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9467</v>
+        <v>1.1507</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8078</v>
+        <v>-0.3869</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6722</v>
+        <v>1.9831</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4246</v>
+        <v>2.6514</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7524</v>
+        <v>-0.6683</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3567</v>
@@ -766,13 +766,13 @@
         <v>1.1903</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1331</v>
+        <v>1.444</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9977</v>
+        <v>1.2244</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1354</v>
+        <v>0.2196</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2945</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0968</v>
+        <v>1.2954</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5354</v>
+        <v>1.7621</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4386</v>
+        <v>-0.4666</v>
       </c>
       <c r="G5" t="n">
         <v>1.9615</v>
@@ -844,13 +844,13 @@
         <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>0.191</v>
+        <v>0.3897</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1304</v>
+        <v>0.3572</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0606</v>
+        <v>0.0325</v>
       </c>
       <c r="V5" t="n">
         <v>2.1184</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0859</v>
+        <v>0.8538</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6876</v>
+        <v>0.4835</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3984</v>
+        <v>0.3703</v>
       </c>
       <c r="G6" t="n">
         <v>-0.5051</v>
@@ -922,13 +922,13 @@
         <v>1.5871</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9959</v>
+        <v>0.7638</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0714</v>
+        <v>0.8673</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.1035</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. RIU GARCIA</t>
+          <t>E. IBAEZ ALDAZABAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.3291</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3421</v>
+        <v>2.482</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6853</v>
+        <v>-2.1529</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0652</v>
+        <v>2.3712</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6299</v>
+        <v>-0.5295</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4353</v>
+        <v>2.9007</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9249</v>
+        <v>5.1516</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0388</v>
+        <v>0.1263</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8861</v>
+        <v>5.0253</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.9901</v>
+        <v>-2.7804</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6687</v>
+        <v>-0.6558</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3214</v>
+        <v>-2.1246</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1903</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1984</v>
+        <v>-3.1741</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="S7" t="n">
-        <v>2.0326</v>
+        <v>0.1446</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6155</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4171</v>
+        <v>-0.36</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.501</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.501</v>
+        <v>-0.7979000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>U. SANCHEZ MARTE</t>
+          <t>R. RIU GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0623</v>
+        <v>0.0469</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0623</v>
+        <v>2.9566</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-2.9097</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-1.0652</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0.6299</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-0.4353</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.9249</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.0388</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.8861</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-2.9901</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-1.6687</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-1.3214</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.1903</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.3887</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0623</v>
+        <v>1.4227</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0623</v>
+        <v>1.2301</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.1926</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.501</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.501</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. IBAEZ ALDAZABAL</t>
+          <t>U. SANCHEZ MARTE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7575</v>
+        <v>-0.0623</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5637</v>
+        <v>-0.0623</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3212</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3712</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5295</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9007</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>5.1516</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1263</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>5.0253</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.7804</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6558</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.1246</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3887</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1741</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7855</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-0.0623</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4137</v>
+        <v>-0.0623</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5283</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7979000000000001</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7979000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8966</v>
+        <v>-0.754</v>
       </c>
       <c r="E10" t="n">
-        <v>1.6639</v>
+        <v>1.8907</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5605</v>
+        <v>-2.6447</v>
       </c>
       <c r="G10" t="n">
         <v>0.4203</v>
@@ -1234,13 +1234,13 @@
         <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1185</v>
+        <v>0.0241</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.238</v>
+        <v>-0.0113</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1196</v>
+        <v>0.0354</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6032</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9197</v>
+        <v>-0.9149</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2858</v>
+        <v>1.2065</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2055</v>
+        <v>-2.1213</v>
       </c>
       <c r="G11" t="n">
         <v>0.3778</v>
@@ -1312,13 +1312,13 @@
         <v>0.7935</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4019</v>
+        <v>0.4067</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4422</v>
+        <v>0.3628</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0403</v>
+        <v>0.0439</v>
       </c>
       <c r="V11" t="n">
         <v>-1.501</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9061</v>
+        <v>-2.5541</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1336</v>
+        <v>-0.7255</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7725</v>
+        <v>-1.8286</v>
       </c>
       <c r="G12" t="n">
         <v>-2.9036</v>
@@ -1390,13 +1390,13 @@
         <v>1.9838</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5816</v>
+        <v>-0.2296</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3514</v>
+        <v>0.0567</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2302</v>
+        <v>-0.2863</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2065</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.486599999999999</v>
+        <v>7.110100000000003</v>
       </c>
       <c r="E13" t="n">
-        <v>21.3215</v>
+        <v>21.9451</v>
       </c>
       <c r="F13" t="n">
-        <v>-14.8348</v>
+        <v>-14.8349</v>
       </c>
       <c r="G13" t="n">
         <v>4.287199999999999</v>
@@ -1468,13 +1468,13 @@
         <v>13.887</v>
       </c>
       <c r="S13" t="n">
-        <v>6.065000000000001</v>
+        <v>6.688600000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>6.6326</v>
+        <v>7.2559</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5673999999999999</v>
+        <v>-0.5675</v>
       </c>
       <c r="V13" t="n">
         <v>-2.873699999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2756</v>
+        <v>6.3316</v>
       </c>
       <c r="E14" t="n">
-        <v>9.856400000000001</v>
+        <v>10.6726</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.5808</v>
+        <v>-4.3411</v>
       </c>
       <c r="G14" t="n">
         <v>3.3187</v>
@@ -1546,13 +1546,13 @@
         <v>2.579</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8411</v>
+        <v>-0.7851</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0599</v>
+        <v>-0.2436</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7812</v>
+        <v>-0.5414</v>
       </c>
       <c r="V14" t="n">
         <v>2.6076</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0408</v>
+        <v>2.7849</v>
       </c>
       <c r="E15" t="n">
-        <v>5.6267</v>
+        <v>5.0145</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5859</v>
+        <v>-2.2296</v>
       </c>
       <c r="G15" t="n">
         <v>3.5685</v>
@@ -1624,13 +1624,13 @@
         <v>1.3887</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0675</v>
+        <v>-0.1885</v>
       </c>
       <c r="T15" t="n">
-        <v>0.924</v>
+        <v>0.3118</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8565</v>
+        <v>-0.5003</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9454</v>
+        <v>1.9591</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1858</v>
+        <v>2.0635</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2404</v>
+        <v>-0.1044</v>
       </c>
       <c r="G16" t="n">
         <v>0.86</v>
@@ -1702,13 +1702,13 @@
         <v>1.3887</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6211</v>
+        <v>0.6348</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7289</v>
+        <v>0.6065</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1077</v>
+        <v>0.0283</v>
       </c>
       <c r="V16" t="n">
         <v>0.266</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2331</v>
+        <v>1.007</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5798</v>
+        <v>2.2737</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3467</v>
+        <v>-1.2667</v>
       </c>
       <c r="G17" t="n">
         <v>1.4114</v>
@@ -1780,13 +1780,13 @@
         <v>0.7935</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2347</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2438</v>
+        <v>-0.0623</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0091</v>
+        <v>0.0708</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2065</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7113</v>
+        <v>-0.3032</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1177</v>
+        <v>0.5259</v>
       </c>
       <c r="F18" t="n">
         <v>-0.8290999999999999</v>
@@ -1858,10 +1858,10 @@
         <v>0.7935</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5442</v>
+        <v>-0.136</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3117</v>
+        <v>0.0964</v>
       </c>
       <c r="U18" t="n">
         <v>-0.2324</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ALEXANDRE</t>
+          <t>D. FONT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6217</v>
+        <v>-2.6542</v>
       </c>
       <c r="E19" t="n">
-        <v>1.245</v>
+        <v>-0.9525</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.8667</v>
+        <v>-1.7017</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8764</v>
+        <v>-2.0066</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8065</v>
+        <v>-1.8952</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6828</v>
+        <v>-0.1114</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6335</v>
+        <v>0.3738</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7901</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8434</v>
+        <v>1.21</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.5099</v>
+        <v>-2.3804</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9837</v>
+        <v>-1.059</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.5262</v>
+        <v>-1.3214</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5871</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1741</v>
+        <v>-1.1903</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5044999999999999</v>
+        <v>-0.6476</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7856</v>
+        <v>-0.136</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.2811</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3373</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. FONT RODRIGUEZ</t>
+          <t>A. ALEXANDRE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4866</v>
+        <v>-2.7313</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5647</v>
+        <v>-0.1834</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9219</v>
+        <v>-2.5478</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0066</v>
+        <v>-0.8764</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8952</v>
+        <v>0.8065</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1114</v>
+        <v>-1.6828</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3738</v>
+        <v>2.6335</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8362000000000001</v>
+        <v>1.7901</v>
       </c>
       <c r="L20" t="n">
-        <v>1.21</v>
+        <v>0.8434</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3804</v>
+        <v>-3.5099</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.059</v>
+        <v>-0.9837</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3214</v>
+        <v>-2.5262</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1903</v>
+        <v>-3.1741</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1903</v>
+        <v>1.5871</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.48</v>
+        <v>-0.6051</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7481</v>
+        <v>0.3572</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7318</v>
+        <v>-0.9623</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.3373</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X. GUIA HORMIGON</t>
+          <t>M. ESTEBAN CALVO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8254</v>
+        <v>-3.3957</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7164</v>
+        <v>-1.9252</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.109</v>
+        <v>-1.4705</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2754</v>
+        <v>-4.2926</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1509</v>
+        <v>-0.9126</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1245</v>
+        <v>-3.3801</v>
       </c>
       <c r="J21" t="n">
-        <v>0.318</v>
+        <v>-1.6532</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9179</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5999</v>
+        <v>-1.1194</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5934</v>
+        <v>-2.6395</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0688</v>
+        <v>-0.3788</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-2.2607</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5952</v>
+        <v>1.7855</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.1984</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7935</v>
+        <v>1.9838</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9982</v>
+        <v>-0.8885</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4988</v>
+        <v>-0.0736</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4994</v>
+        <v>-0.8149</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.1469</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3373</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. ESTEBAN CALVO</t>
+          <t>X. GUIA HORMIGON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4202</v>
+        <v>-3.4011</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5374</v>
+        <v>-0.5123</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8828</v>
+        <v>-2.8888</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.2926</v>
+        <v>-1.2754</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9126</v>
+        <v>-0.1509</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.3801</v>
+        <v>-1.1245</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.6532</v>
+        <v>0.318</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5338000000000001</v>
+        <v>0.9179</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1194</v>
+        <v>-0.5999</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.6395</v>
+        <v>-1.5934</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3788</v>
+        <v>-1.0688</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.2607</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>1.7855</v>
+        <v>0.5952</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.1984</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9838</v>
+        <v>0.7935</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.913</v>
+        <v>-0.5739</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6858</v>
+        <v>-0.2947</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.2272</v>
+        <v>-0.2792</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-2.1469</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9163</v>
+        <v>-3.9964</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3549</v>
+        <v>-1.5387</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5614</v>
+        <v>-2.4577</v>
       </c>
       <c r="G23" t="n">
         <v>-4.2323</v>
@@ -2248,13 +2248,13 @@
         <v>2.3806</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7164</v>
+        <v>-0.7964</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8105</v>
+        <v>0.0057</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9059</v>
+        <v>-0.8022</v>
       </c>
       <c r="V23" t="n">
         <v>3.0162</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.4866</v>
+        <v>-4.399300000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>15.438</v>
+        <v>15.4381</v>
       </c>
       <c r="F24" t="n">
-        <v>-21.9247</v>
+        <v>-19.8374</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.287000000000001</v>
+        <v>-4.287000000000002</v>
       </c>
       <c r="H24" t="n">
-        <v>3.097500000000001</v>
+        <v>3.0975</v>
       </c>
       <c r="I24" t="n">
         <v>-7.384600000000001</v>
@@ -2317,7 +2317,7 @@
         <v>-17.9427</v>
       </c>
       <c r="P24" t="n">
-        <v>0.992</v>
+        <v>0.9920000000000004</v>
       </c>
       <c r="Q24" t="n">
         <v>-13.8869</v>
@@ -2326,13 +2326,13 @@
         <v>14.8787</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.0651</v>
+        <v>-3.9778</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5675000000000001</v>
+        <v>0.5674000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.6323</v>
+        <v>-4.5452</v>
       </c>
       <c r="V24" t="n">
         <v>2.8737</v>
